--- a/outputs/daily/hr_rankings_2026-10-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-10.xlsx
@@ -840,7 +840,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -891,7 +891,7 @@
         <v>38.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -905,39 +905,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1082,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1158,7 +1154,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1182,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1196,7 +1192,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1209,7 +1205,7 @@
         <v>38.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1223,39 +1219,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1400,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1476,7 +1468,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1500,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53.9</v>
+        <v>54.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1514,7 +1506,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1527,7 +1519,7 @@
         <v>38.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1541,39 +1533,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1718,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1794,7 +1782,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1818,7 +1806,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.7</v>
+        <v>54.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1832,7 +1820,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1845,7 +1833,7 @@
         <v>38.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -1859,39 +1847,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2036,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2112,7 +2096,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2136,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.7</v>
+        <v>52.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2150,7 +2134,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -2163,7 +2147,7 @@
         <v>38.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -2177,39 +2161,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -2354,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2430,7 +2410,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2454,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2468,7 +2448,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2481,7 +2461,7 @@
         <v>38.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2495,39 +2475,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2672,7 +2648,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2723,24 +2699,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -2748,22 +2724,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2772,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>49.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2786,26 +2762,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R8" t="n">
         <v>38.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -2813,39 +2789,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2865,12 +2837,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2880,117 +2852,117 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3041,24 +3013,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -3066,22 +3038,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3090,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3104,26 +3076,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.9</v>
+        <v>36.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.7</v>
+        <v>47</v>
       </c>
       <c r="R9" t="n">
         <v>38.6</v>
       </c>
       <c r="S9" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -3131,39 +3103,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3183,12 +3151,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -3198,117 +3166,117 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3384,7 +3352,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3408,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3422,7 +3390,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3435,7 +3403,7 @@
         <v>38.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3449,39 +3417,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3626,7 +3590,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3682,7 +3646,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3702,7 +3666,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3726,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3740,7 +3704,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3753,7 +3717,7 @@
         <v>38.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -3767,39 +3731,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3944,7 +3904,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -3995,24 +3955,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -4020,7 +3980,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -4030,12 +3990,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -4044,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.3</v>
+        <v>45.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4058,26 +4018,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
         <v>38.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -4085,42 +4045,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -4137,132 +4093,132 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4313,24 +4269,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -4338,22 +4294,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4362,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4376,26 +4332,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
         <v>38.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -4403,39 +4359,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4455,7 +4407,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -4465,122 +4417,122 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4631,12 +4583,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4656,7 +4608,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4680,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4694,26 +4646,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
         <v>38.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -4721,42 +4673,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -4773,7 +4721,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -4783,17 +4731,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -4803,67 +4751,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -4898,7 +4846,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4974,7 +4922,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4998,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -5012,7 +4960,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -5025,7 +4973,7 @@
         <v>38.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -5039,39 +4987,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5216,7 +5160,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5267,24 +5211,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -5292,22 +5236,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5316,7 +5260,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5330,26 +5274,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
         <v>38.6</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>43.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -5357,39 +5301,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5409,132 +5349,132 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5585,12 +5525,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5610,12 +5550,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5634,7 +5574,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5648,11 +5588,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
         <v>47</v>
@@ -5661,13 +5601,13 @@
         <v>38.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -5675,42 +5615,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -5727,12 +5663,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5742,7 +5678,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -5757,67 +5693,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -5852,7 +5788,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5903,24 +5839,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -5928,22 +5864,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5952,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.2</v>
+        <v>38.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5966,26 +5902,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
         <v>38.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -5993,39 +5929,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6050,7 +5982,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -6065,112 +5997,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6221,12 +6153,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -6246,12 +6178,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -6270,7 +6202,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6284,26 +6216,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
         <v>38.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -6311,39 +6243,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6363,27 +6291,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -6393,67 +6321,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -6488,7 +6416,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6970,7 +6898,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6994,7 +6922,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -7008,7 +6936,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -7021,7 +6949,7 @@
         <v>38.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -7035,39 +6963,35 @@
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7212,7 +7136,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7288,7 +7212,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -7312,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>55.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7326,7 +7250,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -7339,7 +7263,7 @@
         <v>38.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -7353,39 +7277,35 @@
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7530,7 +7450,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7606,7 +7526,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -7630,7 +7550,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>53.9</v>
+        <v>54.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7644,7 +7564,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -7657,7 +7577,7 @@
         <v>38.6</v>
       </c>
       <c r="S4" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -7671,39 +7591,35 @@
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7848,7 +7764,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7924,7 +7840,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7948,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>53.7</v>
+        <v>54.3</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7962,7 +7878,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7975,7 +7891,7 @@
         <v>38.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>50</v>
@@ -7989,39 +7905,35 @@
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8166,7 +8078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8242,7 +8154,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -8266,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>51.7</v>
+        <v>52.3</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8280,7 +8192,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -8293,7 +8205,7 @@
         <v>38.6</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -8307,39 +8219,35 @@
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8484,7 +8392,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8560,7 +8468,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -8584,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>50.9</v>
+        <v>51.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8598,7 +8506,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -8611,7 +8519,7 @@
         <v>38.6</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -8625,39 +8533,35 @@
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8802,7 +8706,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8853,24 +8757,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -8878,22 +8782,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -8902,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>48.3</v>
+        <v>49.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8916,26 +8820,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R8" t="n">
         <v>38.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T8" t="n">
         <v>80</v>
       </c>
       <c r="U8" t="n">
-        <v>10.1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>50</v>
@@ -8943,39 +8847,35 @@
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8995,12 +8895,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -9010,117 +8910,117 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9171,24 +9071,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -9196,22 +9096,22 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -9220,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9234,26 +9134,26 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>49.9</v>
+        <v>36.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>54.7</v>
+        <v>47</v>
       </c>
       <c r="R9" t="n">
         <v>38.6</v>
       </c>
       <c r="S9" t="n">
-        <v>40.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>10.1</v>
       </c>
       <c r="V9" t="n">
         <v>50</v>
@@ -9261,39 +9161,35 @@
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9313,12 +9209,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -9328,117 +9224,117 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9514,7 +9410,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -9538,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9552,7 +9448,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -9565,7 +9461,7 @@
         <v>38.6</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -9579,39 +9475,35 @@
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -9756,7 +9648,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9812,7 +9704,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -9832,7 +9724,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -9856,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>46.8</v>
+        <v>47.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9870,7 +9762,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -9883,7 +9775,7 @@
         <v>38.6</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>75</v>
@@ -9897,39 +9789,35 @@
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10074,7 +9962,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10125,24 +10013,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -10150,7 +10038,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10160,12 +10048,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -10174,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>44.3</v>
+        <v>45.7</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10188,26 +10076,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>53.5</v>
+        <v>44.9</v>
       </c>
       <c r="R12" t="n">
         <v>38.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T12" t="n">
         <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V12" t="n">
         <v>50</v>
@@ -10215,42 +10103,38 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -10267,132 +10151,132 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10443,24 +10327,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>686668</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Brenton Doyle</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -10468,22 +10352,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -10492,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.4</v>
+        <v>43.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10506,26 +10390,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>44.9</v>
+        <v>54.7</v>
       </c>
       <c r="R13" t="n">
         <v>38.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>82</v>
       </c>
       <c r="V13" t="n">
         <v>50</v>
@@ -10533,39 +10417,35 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10585,7 +10465,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -10595,122 +10475,122 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>38.23</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>99.9948</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.3394</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1259</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.2615</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>72.03</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>15.93</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>37.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1332</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10761,12 +10641,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -10786,7 +10666,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -10810,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>43.2</v>
+        <v>42.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10824,26 +10704,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>20.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R14" t="n">
         <v>38.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>12</v>
       </c>
       <c r="V14" t="n">
         <v>50</v>
@@ -10851,42 +10731,38 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
@@ -10903,7 +10779,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -10913,17 +10789,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -10933,67 +10809,67 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -11028,7 +10904,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11104,7 +10980,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -11128,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>41.4</v>
+        <v>42</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11142,7 +11018,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -11155,7 +11031,7 @@
         <v>38.6</v>
       </c>
       <c r="S15" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
@@ -11169,39 +11045,35 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11346,7 +11218,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11397,24 +11269,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -11422,22 +11294,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sean Burke</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>680732</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -11446,7 +11318,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11460,26 +11332,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.9</v>
+        <v>13.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>47</v>
+        <v>54.7</v>
       </c>
       <c r="R16" t="n">
         <v>38.6</v>
       </c>
       <c r="S16" t="n">
-        <v>88.7</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>43.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>50</v>
@@ -11487,39 +11359,35 @@
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11539,132 +11407,132 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>10.68</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>39.97</t>
+          <t>45.91</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>90.26</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.3987</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>0.1648</t>
+          <t>0.1761</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11715,12 +11583,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11740,12 +11608,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -11764,7 +11632,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11778,11 +11646,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q17" t="n">
         <v>47</v>
@@ -11791,13 +11659,13 @@
         <v>38.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V17" t="n">
         <v>50</v>
@@ -11805,42 +11673,38 @@
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
@@ -11857,12 +11721,12 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -11872,7 +11736,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -11887,67 +11751,67 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -11982,7 +11846,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -12033,24 +11897,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-11T00:00:00Z</t>
@@ -12058,22 +11922,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sean Burke</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>680732</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -12082,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>39.2</v>
+        <v>38.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -12096,26 +11960,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>54.7</v>
+        <v>44.9</v>
       </c>
       <c r="R18" t="n">
         <v>38.6</v>
       </c>
       <c r="S18" t="n">
-        <v>47.9</v>
+        <v>44.8</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U18" t="n">
-        <v>77.40000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="V18" t="n">
         <v>50</v>
@@ -12123,39 +11987,35 @@
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12180,7 +12040,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -12195,112 +12055,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 26.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>10.68</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>45.91</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>90.26</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.3987</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>0.1761</t>
+          <t>0.1648</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>30.98</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12351,12 +12211,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -12376,12 +12236,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12400,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12414,26 +12274,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>13.7</v>
+        <v>7.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44.9</v>
+        <v>47</v>
       </c>
       <c r="R19" t="n">
         <v>38.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>72.7</v>
+        <v>38.3</v>
       </c>
       <c r="V19" t="n">
         <v>50</v>
@@ -12441,39 +12301,35 @@
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12493,27 +12349,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 20.2 HR allowed</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -12523,67 +12379,67 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>70.22</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -12618,7 +12474,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>100 deg</t>
+          <t>Varies</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-10.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-10.xlsx
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.3</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -888,7 +888,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.6</v>
+        <v>56.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1516,7 +1516,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>56.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2120,7 +2120,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.3</v>
+        <v>54.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.5</v>
+        <v>53.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -2748,7 +2748,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.7</v>
+        <v>51.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -2962,7 +2962,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>50.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.9</v>
+        <v>49.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -3690,7 +3690,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.4</v>
+        <v>49.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -4004,7 +4004,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>47.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -4318,7 +4318,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>45.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -4946,7 +4946,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42</v>
+        <v>43.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -5260,7 +5260,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -5474,7 +5474,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5598,7 +5598,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -5788,7 +5788,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -5888,7 +5888,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>40.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -6102,7 +6102,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.6</v>
+        <v>38.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6226,7 +6226,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -6922,11 +6922,11 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>68.3</v>
+        <v>70.2</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tier 3</t>
+          <t>Tier 2</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -6946,7 +6946,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.6</v>
+        <v>57.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>54.7</v>
       </c>
       <c r="R3" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -7450,7 +7450,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -7550,7 +7550,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>54.6</v>
+        <v>56.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>54.7</v>
       </c>
       <c r="R4" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -7864,7 +7864,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>54.3</v>
+        <v>56.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>47</v>
       </c>
       <c r="R5" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S5" t="n">
         <v>94.90000000000001</v>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>52.3</v>
+        <v>54.2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>47</v>
       </c>
       <c r="R6" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S6" t="n">
         <v>96.59999999999999</v>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>51.5</v>
+        <v>53.4</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S7" t="n">
         <v>86.40000000000001</v>
@@ -8706,7 +8706,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>49.7</v>
+        <v>51.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         <v>54.7</v>
       </c>
       <c r="R8" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S8" t="n">
         <v>52.4</v>
@@ -9020,7 +9020,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -9120,7 +9120,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>49</v>
+        <v>50.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>47</v>
       </c>
       <c r="R9" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S9" t="n">
         <v>86.40000000000001</v>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -9434,7 +9434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>47.9</v>
+        <v>49.8</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S10" t="n">
         <v>93.2</v>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>47.4</v>
+        <v>49.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>44.9</v>
       </c>
       <c r="R11" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S11" t="n">
         <v>100</v>
@@ -9962,7 +9962,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -10062,7 +10062,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>45.7</v>
+        <v>47.6</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>44.9</v>
       </c>
       <c r="R12" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S12" t="n">
         <v>64.3</v>
@@ -10276,7 +10276,7 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
@@ -10376,7 +10376,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>43.8</v>
+        <v>45.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -10590,7 +10590,7 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>42.9</v>
+        <v>44.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v>47</v>
       </c>
       <c r="R14" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S14" t="n">
         <v>76.2</v>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>42</v>
+        <v>43.9</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S15" t="n">
         <v>76.2</v>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -11318,7 +11318,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>41.4</v>
+        <v>43.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>54.7</v>
       </c>
       <c r="R16" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S16" t="n">
         <v>64.3</v>
@@ -11532,7 +11532,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -11632,7 +11632,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>41.2</v>
+        <v>43.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>47</v>
       </c>
       <c r="R17" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S17" t="n">
         <v>93.2</v>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -11946,7 +11946,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>38.4</v>
+        <v>40.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44.9</v>
       </c>
       <c r="R18" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S18" t="n">
         <v>44.8</v>
@@ -12160,7 +12160,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -12260,7 +12260,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>36.6</v>
+        <v>38.5</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>47</v>
       </c>
       <c r="R19" t="n">
-        <v>38.6</v>
+        <v>52.1</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
